--- a/user-list.xlsx
+++ b/user-list.xlsx
@@ -4,13 +4,14 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12255"/>
+    <workbookView windowWidth="27945" windowHeight="12255" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Users" sheetId="1" r:id="rId1"/>
+    <sheet name="人员" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Users!$A$1:$B$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Users!$A$1:$B$10</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -30,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="21">
   <si>
     <t>人名</t>
   </si>
@@ -38,28 +39,43 @@
     <t>城市名</t>
   </si>
   <si>
+    <t>仇红建</t>
+  </si>
+  <si>
+    <t>长春</t>
+  </si>
+  <si>
     <t>曹洋</t>
   </si>
   <si>
-    <t>长春</t>
+    <t>李智</t>
+  </si>
+  <si>
+    <t>济南</t>
   </si>
   <si>
     <t>汪步江</t>
   </si>
   <si>
-    <t>济南</t>
+    <t>张俊</t>
+  </si>
+  <si>
+    <t>武汉</t>
   </si>
   <si>
     <t>张志琪</t>
   </si>
   <si>
-    <t>武汉</t>
+    <t>刘庆钊</t>
+  </si>
+  <si>
+    <t>北京</t>
   </si>
   <si>
     <t>冯亚南</t>
   </si>
   <si>
-    <t>北京</t>
+    <t>万成军</t>
   </si>
   <si>
     <t>侯文杰</t>
@@ -68,13 +84,16 @@
     <t>丁凯云</t>
   </si>
   <si>
+    <t>王方圆</t>
+  </si>
+  <si>
     <t>刘康</t>
   </si>
   <si>
     <t>林阳</t>
   </si>
   <si>
-    <t>李智</t>
+    <t>姓名</t>
   </si>
 </sst>
 </file>
@@ -87,7 +106,7 @@
     <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
   </numFmts>
-  <fonts count="24">
+  <fonts count="23">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -114,13 +133,6 @@
       <color rgb="FF333333"/>
       <name val="微软雅黑"/>
       <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <u/>
@@ -635,133 +647,133 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="8" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="8" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -781,7 +793,7 @@
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1307,7 +1319,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:T10"/>
+  <dimension ref="A1:T15"/>
   <sheetFormatPr defaultColWidth="8.725" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="13.0916666666667" customWidth="1"/>
@@ -1341,13 +1353,15 @@
       <c r="T1" s="2"/>
     </row>
     <row r="2" ht="16.5" spans="1:20">
-      <c r="A2" s="3" t="s">
+      <c r="A2" t="s">
         <v>2</v>
       </c>
       <c r="B2" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="C2" s="2"/>
+      <c r="C2" s="3" t="s">
+        <v>4</v>
+      </c>
       <c r="D2" s="2"/>
       <c r="E2" s="2"/>
       <c r="F2" s="2"/>
@@ -1367,13 +1381,15 @@
       <c r="T2" s="2"/>
     </row>
     <row r="3" ht="16.5" spans="1:20">
-      <c r="A3" s="4" t="s">
-        <v>4</v>
+      <c r="A3" t="s">
+        <v>5</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="C3" s="2"/>
+        <v>6</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>7</v>
+      </c>
       <c r="D3" s="2"/>
       <c r="E3" s="2"/>
       <c r="F3" s="2"/>
@@ -1393,13 +1409,15 @@
       <c r="T3" s="2"/>
     </row>
     <row r="4" ht="16.5" spans="1:20">
-      <c r="A4" s="4" t="s">
-        <v>6</v>
+      <c r="A4" t="s">
+        <v>8</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C4" s="2"/>
+        <v>9</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>10</v>
+      </c>
       <c r="D4" s="2"/>
       <c r="E4" s="2"/>
       <c r="F4" s="2"/>
@@ -1420,45 +1438,137 @@
     </row>
     <row r="5" ht="16.5" spans="1:20">
       <c r="A5" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>9</v>
+        <v>12</v>
+      </c>
+      <c r="C5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="6" ht="16.5" spans="1:20">
       <c r="A6" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>9</v>
+        <v>12</v>
+      </c>
+      <c r="C6" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="7" spans="1:20">
-      <c r="A7" s="5" t="s">
-        <v>11</v>
+      <c r="A7" t="s">
+        <v>2</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="8" spans="1:20">
       <c r="A8" t="s">
-        <v>12</v>
+        <v>17</v>
+      </c>
+      <c r="C8" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="9" spans="1:20">
-      <c r="A9" t="s">
-        <v>13</v>
+      <c r="C9" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="10" spans="1:20">
-      <c r="A10" t="s">
+      <c r="C10" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:20">
+      <c r="C11" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="12" spans="1:20">
+      <c r="C12" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="13" spans="1:20">
+      <c r="C13" t="s">
         <v>14</v>
       </c>
     </row>
+    <row r="14" spans="1:20">
+      <c r="C14" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:20">
+      <c r="C15" t="s">
+        <v>17</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:B5" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:B10" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:A8"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="7"/>
+  <cols>
+    <col min="1" max="1" width="13.0916666666667" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="15" spans="1:1">
+      <c r="A1" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1">
+      <c r="A2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1">
+      <c r="A3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1">
+      <c r="A4" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1">
+      <c r="A5" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1">
+      <c r="A6" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1">
+      <c r="A7" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1">
+      <c r="A8" t="s">
+        <v>17</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
 </file>